--- a/tests/corpus/scenario/data/조달_한글.xlsx
+++ b/tests/corpus/scenario/data/조달_한글.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입찰건" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,30 +498,35 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>개찰일시</t>
+          <t>개찰일자</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>개찰시각</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>등록마감일시</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>담당부서</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>담당자 전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>세부품명번호</t>
         </is>
@@ -611,30 +615,35 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-22 10:00</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>2026-07-21 17:00</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>장비구매팀</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>김담당</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>044-200-1234</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>1234567890</t>
         </is>
@@ -723,30 +732,35 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>2026-07-22 17:00</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>연구지원팀</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>박담당</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>051-720-5678</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>9876543210</t>
         </is>
@@ -835,30 +849,35 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-07-26 10:00</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>2026-07-25 17:00</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>정보화담당관</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>이담당</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>051-609-8765</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>5555512345</t>
         </is>

--- a/tests/corpus/scenario/data/조달_한글.xlsx
+++ b/tests/corpus/scenario/data/조달_한글.xlsx
@@ -488,45 +488,55 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>입찰개시일시</t>
+          <t>입찰개시일자</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>입찰마감일시</t>
+          <t>입찰개시시각</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>입찰마감일자</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>입찰마감시각</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>개찰일자</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>개찰시각</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>등록마감일시</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>담당부서</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>담당자 전화번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>세부품명번호</t>
         </is>
@@ -605,45 +615,55 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:00</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>2026-07-21 17:00</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-07-21 17:00</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>장비구매팀</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>김담당</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>044-200-1234</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>1234567890</t>
         </is>
@@ -722,45 +742,55 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-07-16 09:00</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>2026-07-22 17:00</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-07-22 17:00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>연구지원팀</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>박담당</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>051-720-5678</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>9876543210</t>
         </is>
@@ -839,45 +869,55 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-07-18 09:00</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>2026-07-25 17:00</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-07-25 17:00</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>정보화담당관</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>이담당</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>051-609-8765</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>5555512345</t>
         </is>
